--- a/UPSC-Evaluator/public/samples/student-sheet.xlsx
+++ b/UPSC-Evaluator/public/samples/student-sheet.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAM\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18870" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,23 +19,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Name</t>
   </si>
@@ -47,33 +36,35 @@
   </si>
   <si>
     <t>Unique Id</t>
+  </si>
+  <si>
+    <t>Mayank Pipaliya</t>
+  </si>
+  <si>
+    <t>mayank@gmail.com</t>
+  </si>
+  <si>
+    <t>AT101</t>
+  </si>
+  <si>
+    <t>Kevin Gondaliya</t>
+  </si>
+  <si>
+    <t>kevin@gmail.com</t>
+  </si>
+  <si>
+    <t>AT102</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -95,17 +86,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -132,39 +120,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -197,26 +185,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -249,23 +220,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -327,6 +281,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -335,13 +296,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -406,31 +360,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -438,58 +372,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="24.5" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="C2" s="2"/>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1">
+        <v>9737237543</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="C11" s="2"/>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1">
+        <v>9638036556</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
